--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Acte</t>
+    <t>Entrée Acte</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -406,15 +406,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
   </si>
   <si>
     <t>fr-lm-procedure.status</t>
@@ -933,7 +924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.6484375" customWidth="true" bestFit="true"/>
@@ -2496,7 +2487,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2547,10 +2538,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2568,10 +2559,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2585,10 +2576,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2614,10 +2605,10 @@
         <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2647,10 +2638,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2668,7 +2659,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2711,13 +2702,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2747,7 +2738,7 @@
         <v>73</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>73</v>
@@ -2780,15 +2771,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2796,7 +2787,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2811,13 +2802,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2868,10 +2859,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2880,26 +2871,26 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>140</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2911,15 +2902,17 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2956,50 +2949,50 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -3011,16 +3004,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3058,39 +3051,39 @@
         <v>73</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3098,7 +3091,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3113,17 +3106,15 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3172,10 +3163,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3184,15 +3175,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3215,13 +3206,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3272,7 +3263,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3284,15 +3275,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3318,10 +3309,10 @@
         <v>117</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3372,7 +3363,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3389,10 +3380,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3415,13 +3406,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3451,7 +3442,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3472,7 +3463,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3651,7 +3642,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3689,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3718,10 +3709,10 @@
         <v>121</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3751,28 +3742,28 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3789,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3803,7 +3794,7 @@
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3815,7 +3806,7 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>181</v>
@@ -3872,13 +3863,13 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
@@ -3903,7 +3894,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3915,13 +3906,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3978,7 +3969,7 @@
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3989,10 +3980,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4003,7 +3994,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4018,10 +4009,10 @@
         <v>121</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4051,7 +4042,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4072,13 +4063,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4115,13 +4106,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4151,7 +4142,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4215,13 +4206,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4289,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4303,7 +4294,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4315,13 +4306,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4372,118 +4363,18 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-procedure.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -1902,13 +1906,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,7 +1963,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1976,10 +1980,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2002,13 +2006,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2059,7 +2063,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2076,10 +2080,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2102,13 +2106,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2159,7 +2163,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2176,10 +2180,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2202,13 +2206,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2259,7 +2263,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2276,10 +2280,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2302,13 +2306,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2359,7 +2363,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2376,10 +2380,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2402,13 +2406,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2459,7 +2463,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2476,10 +2480,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2502,13 +2506,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2538,10 +2542,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2559,7 +2563,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2576,10 +2580,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2602,13 +2606,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2638,7 +2642,7 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -2659,7 +2663,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2676,10 +2680,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2702,13 +2706,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2759,7 +2763,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2771,15 +2775,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2802,13 +2806,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2859,7 +2863,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2876,14 +2880,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -2902,16 +2906,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2949,19 +2953,19 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2973,15 +2977,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3004,16 +3008,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3063,7 +3067,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3080,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3106,13 +3110,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3163,7 +3167,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3175,15 +3179,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3206,13 +3210,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3263,7 +3267,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3280,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3306,13 +3310,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3363,7 +3367,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3380,10 +3384,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3406,13 +3410,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3442,7 +3446,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3463,7 +3467,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3480,10 +3484,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3506,13 +3510,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3542,7 +3546,7 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3563,7 +3567,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3580,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3606,13 +3610,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3642,7 +3646,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3663,7 +3667,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3680,10 +3684,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3706,13 +3710,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3763,7 +3767,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3780,10 +3784,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3806,13 +3810,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3863,7 +3867,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3880,10 +3884,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3906,13 +3910,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3963,7 +3967,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3980,10 +3984,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4006,13 +4010,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4042,7 +4046,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4063,7 +4067,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4080,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4106,13 +4110,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4163,7 +4167,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4180,10 +4184,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4206,13 +4210,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4263,7 +4267,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4280,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4306,13 +4310,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4363,7 +4367,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="204">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-procedure.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-procedure.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-procedure.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-procedure.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-procedure.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-procedure.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-procedure.header.source</t>
+    <t>fr-lm-procedure.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-procedure.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,18 +452,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-procedure.status</t>
-  </si>
-  <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
   </si>
   <si>
     <t>fr-lm-procedure.code</t>
@@ -608,10 +638,6 @@
   </si>
   <si>
     <t>fr-lm-procedure.deviceUsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
-</t>
   </si>
   <si>
     <t>Dispositif médical utilisé pendant l'acte</t>
@@ -928,11 +954,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.6484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.6484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.5703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1706,13 +1732,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1763,7 +1789,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1780,10 +1806,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1806,13 +1832,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1863,7 +1889,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1880,10 +1906,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1906,13 +1932,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1963,7 +1989,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1980,10 +2006,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2006,7 +2032,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2106,13 +2132,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2163,7 +2189,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2180,10 +2206,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2194,7 +2220,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2206,13 +2232,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2263,13 +2289,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2280,10 +2306,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2294,7 +2320,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2306,13 +2332,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2363,13 +2389,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2380,10 +2406,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2394,7 +2420,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2406,13 +2432,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2463,13 +2489,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2480,10 +2506,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2491,7 +2517,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2506,13 +2532,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2542,10 +2568,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2563,10 +2589,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2580,10 +2606,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2606,13 +2632,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2642,11 +2668,11 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
       </c>
@@ -2663,7 +2689,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2680,10 +2706,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2691,7 +2717,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2706,7 +2732,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>137</v>
@@ -2763,10 +2789,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2775,7 +2801,7 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2806,13 +2832,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2863,7 +2889,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2880,21 +2906,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2906,17 +2932,15 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2944,7 +2968,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2953,39 +2977,39 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3008,17 +3032,15 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3067,7 +3089,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3079,15 +3101,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3110,13 +3132,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3167,7 +3189,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3179,26 +3201,26 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3210,15 +3232,17 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3255,39 +3279,39 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3295,7 +3319,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3310,15 +3334,17 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3367,10 +3393,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3410,13 +3436,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3446,7 +3472,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3467,7 +3493,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3479,15 +3505,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3510,13 +3536,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3546,7 +3572,7 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3567,7 +3593,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3584,10 +3610,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3610,13 +3636,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3646,7 +3672,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3667,7 +3693,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3684,10 +3710,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3710,13 +3736,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3746,7 +3772,7 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -3767,7 +3793,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3784,10 +3810,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3798,7 +3824,7 @@
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3810,13 +3836,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3846,7 +3872,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3867,13 +3893,13 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
@@ -3884,10 +3910,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3910,13 +3936,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3946,7 +3972,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3967,7 +3993,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3984,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3998,7 +4024,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4010,13 +4036,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4046,7 +4072,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4067,13 +4093,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4084,10 +4110,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4110,13 +4136,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4167,7 +4193,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4184,10 +4210,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4198,7 +4224,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4210,13 +4236,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4267,13 +4293,13 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
@@ -4284,10 +4310,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4298,7 +4324,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4310,13 +4336,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4346,7 +4372,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4367,18 +4393,318 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -587,6 +587,10 @@
   </si>
   <si>
     <t>fr-lm-procedure.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>localisation anatomique</t>
@@ -3836,13 +3840,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3872,7 +3876,7 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>73</v>
@@ -3910,10 +3914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3939,10 +3943,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3972,7 +3976,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3993,7 +3997,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4010,10 +4014,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4039,10 +4043,10 @@
         <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4093,7 +4097,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4110,10 +4114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4136,13 +4140,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4193,7 +4197,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4210,10 +4214,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4239,10 +4243,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4293,7 +4297,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4310,10 +4314,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4339,10 +4343,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4372,7 +4376,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4393,7 +4397,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4410,10 +4414,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4439,10 +4443,10 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4493,7 +4497,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4510,10 +4514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4539,10 +4543,10 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4593,7 +4597,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4610,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4639,10 +4643,10 @@
         <v>150</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4693,7 +4697,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
